--- a/data/trans_camb/IP1015-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,0</t>
+          <t>-3,63; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
     </row>
@@ -1733,22 +1733,22 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,89</t>
+          <t>-2,12; 0,89</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,0</t>
+          <t>-3,0; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,45</t>
+          <t>-0,88; 0,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,0</t>
+          <t>-1,31; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,39</t>
+          <t>-0,48; 0,41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,28</t>
+          <t>-0,57; 0,27</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,3</t>
+          <t>-0,22; 0,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,14</t>
+          <t>-0,3; 0,13</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-86,04; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Provincia-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,0</t>
+          <t>-5,1; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
     </row>
@@ -1733,22 +1733,22 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,89</t>
+          <t>-2,11; 0,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,0</t>
+          <t>-3,01; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,45</t>
+          <t>-1,08; 0,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,0</t>
+          <t>-1,32; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,41</t>
+          <t>-0,5; 0,36</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,27</t>
+          <t>-0,59; 0,26</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,27</t>
+          <t>-0,23; 0,25</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,13</t>
+          <t>-0,3; 0,14</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,33; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,0</t>
+          <t>-2,41; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,72; 0,89</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,68; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,45</t>
+          <t>-0,89; 0,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,0</t>
+          <t>-1,49; 0,0</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-48,92%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-48,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,27 +1879,27 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>-0,48; 0,39</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-0,57; 0,28</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,34</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 0,36</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,25</t>
+          <t>-0,21; 0,3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-4,92%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-36,2%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-4,92%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-36,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-86,04; —</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
